--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-31 (1).xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-31 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_2DD5D083547A3F0563183211595ED87656CD32B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A41B905C-8716-421F-8572-3A8665DE1A35}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_2DD5D083547A3F0563183211595ED87656CD32B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31C14D2B-047D-40BB-9390-D97A4064F35B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="66">
   <si>
     <t>Data</t>
   </si>
@@ -189,18 +189,6 @@
   </si>
   <si>
     <t>+2.66%</t>
-  </si>
-  <si>
-    <t>Zamalek x Petrojet</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>BULGARIA 1</t>
-  </si>
-  <si>
-    <t>Arda x Botev Vratsa</t>
   </si>
   <si>
     <t>16:00</t>
@@ -332,6 +320,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -619,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -663,10 +655,10 @@
         <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -761,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O20" si="0">IF(N3=1,0.965/(J3-1),-1)</f>
+        <f t="shared" ref="O3:O16" si="0">IF(N3=1,0.965/(J3-1),-1)</f>
         <v>1.0831743181052867E-2</v>
       </c>
     </row>
@@ -971,38 +963,38 @@
         <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
         <v>19</v>
       </c>
       <c r="H8">
-        <v>13.65</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="I8">
-        <v>7.91</v>
+        <v>13.42</v>
       </c>
       <c r="J8">
-        <v>7.55</v>
+        <v>12.82</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N8">
         <v>1</v>
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>0.14732824427480917</v>
+        <v>8.1641285956006768E-2</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -1010,47 +1002,47 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
       </c>
       <c r="H9">
-        <v>8.4499999999999993</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="I9">
-        <v>13.42</v>
+        <v>14.22</v>
       </c>
       <c r="J9">
-        <v>12.82</v>
+        <v>13.58</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="M9" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>8.1641285956006768E-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -1061,10 +1053,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>42</v>
@@ -1076,13 +1068,13 @@
         <v>19</v>
       </c>
       <c r="H10">
-        <v>8.0299999999999994</v>
+        <v>5.87</v>
       </c>
       <c r="I10">
-        <v>14.22</v>
+        <v>20.53</v>
       </c>
       <c r="J10">
-        <v>13.58</v>
+        <v>19.61</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -1094,11 +1086,11 @@
         <v>45</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>5.1853842020419129E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -1115,38 +1107,38 @@
         <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
         <v>19</v>
       </c>
       <c r="H11">
-        <v>5.87</v>
+        <v>10.09</v>
       </c>
       <c r="I11">
-        <v>20.53</v>
+        <v>11</v>
       </c>
       <c r="J11">
-        <v>19.61</v>
+        <v>10.5</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M11" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="N11">
         <v>1</v>
       </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>5.1853842020419129E-2</v>
+        <v>0.10157894736842105</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -1154,47 +1146,47 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
         <v>19</v>
       </c>
       <c r="H12">
-        <v>10.09</v>
+        <v>7.21</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="J12">
-        <v>10.5</v>
+        <v>15.38</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M12" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N12">
         <v>1</v>
       </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>0.10157894736842105</v>
+        <v>6.7107093184979136E-2</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -1202,31 +1194,31 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="G13" t="s">
         <v>19</v>
       </c>
       <c r="H13">
-        <v>14.7</v>
+        <v>18.5</v>
       </c>
       <c r="I13">
-        <v>7.3</v>
+        <v>5.71</v>
       </c>
       <c r="J13">
-        <v>6.97</v>
+        <v>5.45</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -1235,14 +1227,14 @@
         <v>20</v>
       </c>
       <c r="M13" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="N13">
         <v>1</v>
       </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>0.16164154103852596</v>
+        <v>0.21685393258426966</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -1250,13 +1242,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
@@ -1268,13 +1260,13 @@
         <v>19</v>
       </c>
       <c r="H14">
-        <v>9.8699999999999992</v>
+        <v>14.18</v>
       </c>
       <c r="I14">
-        <v>11.27</v>
+        <v>7.59</v>
       </c>
       <c r="J14">
-        <v>10.76</v>
+        <v>7.25</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -1290,7 +1282,7 @@
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>9.8872950819672137E-2</v>
+        <v>0.15439999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -1298,40 +1290,47 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G15" t="s">
         <v>19</v>
       </c>
       <c r="H15">
-        <v>7.21</v>
+        <v>4.63</v>
       </c>
       <c r="I15">
-        <v>16.100000000000001</v>
+        <v>27.55</v>
       </c>
       <c r="J15">
-        <v>15.38</v>
+        <v>26.31</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="M15" t="s">
-        <v>25</v>
+        <v>45</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="0"/>
+        <v>3.812722244172264E-2</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -1339,204 +1338,47 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
         <v>19</v>
       </c>
       <c r="H16">
-        <v>7.56</v>
+        <v>10.09</v>
       </c>
       <c r="I16">
-        <v>15.24</v>
+        <v>11</v>
       </c>
       <c r="J16">
-        <v>14.55</v>
+        <v>10.5</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="M16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17">
-        <v>18.5</v>
-      </c>
-      <c r="I17">
-        <v>5.71</v>
-      </c>
-      <c r="J17">
-        <v>5.45</v>
-      </c>
-      <c r="K17">
-        <v>100</v>
-      </c>
-      <c r="L17" t="s">
-        <v>20</v>
-      </c>
-      <c r="M17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18">
-        <v>14.18</v>
-      </c>
-      <c r="I18">
-        <v>7.59</v>
-      </c>
-      <c r="J18">
-        <v>7.25</v>
-      </c>
-      <c r="K18">
-        <v>100</v>
-      </c>
-      <c r="L18" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19">
-        <v>4.63</v>
-      </c>
-      <c r="I19">
-        <v>27.55</v>
-      </c>
-      <c r="J19">
-        <v>26.31</v>
-      </c>
-      <c r="K19">
-        <v>100</v>
-      </c>
-      <c r="L19" t="s">
-        <v>44</v>
-      </c>
-      <c r="M19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20" t="s">
-        <v>19</v>
-      </c>
-      <c r="H20">
-        <v>10.09</v>
-      </c>
-      <c r="I20">
-        <v>11</v>
-      </c>
-      <c r="J20">
-        <v>10.5</v>
-      </c>
-      <c r="K20">
-        <v>100</v>
-      </c>
-      <c r="L20" t="s">
-        <v>50</v>
-      </c>
-      <c r="M20" t="s">
         <v>51</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="0"/>
+        <v>0.10157894736842105</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-31 (1).xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-31 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_2DD5D083547A3F0563183211595ED87656CD32B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31C14D2B-047D-40BB-9390-D97A4064F35B}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_2DD5D083547A3F0563183211595ED87656CD32B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82371F1D-D8B6-4F23-A6E9-D7B7E7416F3E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="138">
   <si>
     <t>Data</t>
   </si>
@@ -231,6 +231,222 @@
   </si>
   <si>
     <t>P/L</t>
+  </si>
+  <si>
+    <t>21/08/2026</t>
+  </si>
+  <si>
+    <t>SAUDI ARABIA 1</t>
+  </si>
+  <si>
+    <t>Al Riyadh x Al Nassr</t>
+  </si>
+  <si>
+    <t>WOM GERMANY 1</t>
+  </si>
+  <si>
+    <t>Union Berlin W x Bayern Munich W</t>
+  </si>
+  <si>
+    <t>ICELAND 2</t>
+  </si>
+  <si>
+    <t>Aegir x Afturelding</t>
+  </si>
+  <si>
+    <t>GERMANY CUP</t>
+  </si>
+  <si>
+    <t>Hansa Rostock x Stuttgart</t>
+  </si>
+  <si>
+    <t>Trefelin x Caernarfon</t>
+  </si>
+  <si>
+    <t>Holywell x Barry</t>
+  </si>
+  <si>
+    <t>Cardiff Metropolitan x TNS</t>
+  </si>
+  <si>
+    <t>22/08/2026</t>
+  </si>
+  <si>
+    <t>Hull x Manchester Utd</t>
+  </si>
+  <si>
+    <t>Ammanford x Connahs Q.</t>
+  </si>
+  <si>
+    <t>1.FC Nurnberg W x Wolfsburg W</t>
+  </si>
+  <si>
+    <t>NORTHERN IRELAND 2</t>
+  </si>
+  <si>
+    <t>Strabane Athletic x H&amp;W Welders</t>
+  </si>
+  <si>
+    <t>SLOVAKIA 2</t>
+  </si>
+  <si>
+    <t>MFK Bytca x Z. Moravce-Vrable</t>
+  </si>
+  <si>
+    <t>SPAIN 1</t>
+  </si>
+  <si>
+    <t>Espanyol x Real Madrid</t>
+  </si>
+  <si>
+    <t>23/08/2026</t>
+  </si>
+  <si>
+    <t>ESTONIA 2</t>
+  </si>
+  <si>
+    <t>Nomme Kalju U21 x Tartu Welco</t>
+  </si>
+  <si>
+    <t>Westfalia Rhynern x SG Dynamo Dresden</t>
+  </si>
+  <si>
+    <t>NETHERLANDS 1</t>
+  </si>
+  <si>
+    <t>Cambuur x Feyenoord</t>
+  </si>
+  <si>
+    <t>SLOVENIA 2</t>
+  </si>
+  <si>
+    <t>Krsko Posavje x Tabor Sezana</t>
+  </si>
+  <si>
+    <t>Phonix Lubeck x Paderborn</t>
+  </si>
+  <si>
+    <t>BOLIVIA 1</t>
+  </si>
+  <si>
+    <t>Real Oruro x Bolivar</t>
+  </si>
+  <si>
+    <t>Elche x Barcelona</t>
+  </si>
+  <si>
+    <t>24/08/2026</t>
+  </si>
+  <si>
+    <t>Verl x Hamburger SV</t>
+  </si>
+  <si>
+    <t>Altglienicke x Wolfsburg</t>
+  </si>
+  <si>
+    <t>Wurzburger Kickers x FC Koln</t>
+  </si>
+  <si>
+    <t>Hallescher x Schalke</t>
+  </si>
+  <si>
+    <t>25/08/2026</t>
+  </si>
+  <si>
+    <t>Al Ettifaq x Al Nassr</t>
+  </si>
+  <si>
+    <t>ENGLAND CUP</t>
+  </si>
+  <si>
+    <t>Doncaster x Middlesbrough</t>
+  </si>
+  <si>
+    <t>26/08/2026</t>
+  </si>
+  <si>
+    <t>Preston x Everton</t>
+  </si>
+  <si>
+    <t>27/08/2026</t>
+  </si>
+  <si>
+    <t>EUROPA LEAGUE</t>
+  </si>
+  <si>
+    <t>Kauno Zalgiris (LTU) x Besiktas (TUR)</t>
+  </si>
+  <si>
+    <t>Aarhus (DEN) x Benfica (POR)</t>
+  </si>
+  <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t>SOUTH KOREA 2</t>
+  </si>
+  <si>
+    <t>Ansan Greeners x Daegu</t>
+  </si>
+  <si>
+    <t>AUSTRIA 2</t>
+  </si>
+  <si>
+    <t>Kapfenberg x BW Linz</t>
+  </si>
+  <si>
+    <t>Al Khaleej x Al Hilal</t>
+  </si>
+  <si>
+    <t>Holywell x Caernarfon</t>
+  </si>
+  <si>
+    <t>PORTUGAL 1</t>
+  </si>
+  <si>
+    <t>Rio Ave x Sporting CP</t>
+  </si>
+  <si>
+    <t>29/08/2026</t>
+  </si>
+  <si>
+    <t>Croatian HNL</t>
+  </si>
+  <si>
+    <t>NK Istra x Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>Indian Mizoram Premier League</t>
+  </si>
+  <si>
+    <t>MLS FC x Aizawl FC</t>
+  </si>
+  <si>
+    <t>Portuguese Primeira Liga</t>
+  </si>
+  <si>
+    <t>Academico de Viseu x Porto</t>
+  </si>
+  <si>
+    <t>30/08/2026</t>
+  </si>
+  <si>
+    <t>Karmiotissa Polemidion x Pafos FC</t>
+  </si>
+  <si>
+    <t>Cambuur Leeuwarden x FC Twente</t>
+  </si>
+  <si>
+    <t>Kifisia x AEK Athens</t>
+  </si>
+  <si>
+    <t>BOSNIA 1</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina x Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>31/08/2026</t>
   </si>
 </sst>
 </file>
@@ -611,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -705,8 +921,8 @@
         <v>1</v>
       </c>
       <c r="O2">
-        <f>IF(N2=1,0.965/(J2-1),-1)</f>
-        <v>0.1334716459197787</v>
+        <f>IF(N2=1,0.965/(H2-1),-1)</f>
+        <v>8.3189655172413793E-2</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -753,8 +969,8 @@
         <v>1</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O16" si="0">IF(N3=1,0.965/(J3-1),-1)</f>
-        <v>1.0831743181052867E-2</v>
+        <f t="shared" ref="O3:O58" si="0">IF(N3=1,0.965/(H3-1),-1)</f>
+        <v>0.910377358490566</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -802,7 +1018,7 @@
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>5.073606729758149E-2</v>
+        <v>0.20230607966457023</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -850,7 +1066,7 @@
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>6.9524495677233428E-2</v>
+        <v>0.15031152647975077</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -898,7 +1114,7 @@
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>6.0012437810945278E-2</v>
+        <v>0.17262969588550983</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -946,7 +1162,7 @@
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>5.7715311004784692E-2</v>
+        <v>0.1790352504638219</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -994,7 +1210,7 @@
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>8.1641285956006768E-2</v>
+        <v>0.12953020134228188</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -1090,7 +1306,7 @@
       </c>
       <c r="O10">
         <f t="shared" si="0"/>
-        <v>5.1853842020419129E-2</v>
+        <v>0.19815195071868583</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -1138,7 +1354,7 @@
       </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>0.10157894736842105</v>
+        <v>0.10616061606160616</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -1186,7 +1402,7 @@
       </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>6.7107093184979136E-2</v>
+        <v>0.15539452495974235</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -1234,7 +1450,7 @@
       </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>0.21685393258426966</v>
+        <v>5.5142857142857139E-2</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -1282,7 +1498,7 @@
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>0.15439999999999998</v>
+        <v>7.3216995447647953E-2</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -1330,7 +1546,7 @@
       </c>
       <c r="O15">
         <f t="shared" si="0"/>
-        <v>3.812722244172264E-2</v>
+        <v>0.26584022038567495</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -1378,7 +1594,1267 @@
       </c>
       <c r="O16">
         <f t="shared" si="0"/>
-        <v>0.10157894736842105</v>
+        <v>0.10616061606160616</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17">
+        <v>5.92</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="0"/>
+        <v>0.19613821138211382</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18">
+        <v>6.39</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="0"/>
+        <v>0.1790352504638219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19">
+        <v>8.24</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="0"/>
+        <v>0.13328729281767954</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20">
+        <v>6.18</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="0"/>
+        <v>0.18629343629343631</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21">
+        <v>5.66</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="0"/>
+        <v>0.20708154506437768</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22">
+        <v>5.15</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="0"/>
+        <v>0.23253012048192767</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23">
+        <v>5.66</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="0"/>
+        <v>0.20708154506437768</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24">
+        <v>5.15</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="0"/>
+        <v>0.23253012048192767</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="0"/>
+        <v>0.24807197943444731</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26">
+        <v>5.77</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="0"/>
+        <v>0.20230607966457023</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27">
+        <v>5.15</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="0"/>
+        <v>0.23253012048192767</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="0"/>
+        <v>0.26510989010989011</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" t="s">
+        <v>43</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29">
+        <v>5.15</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="0"/>
+        <v>0.23253012048192767</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" t="s">
+        <v>43</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30">
+        <v>7.21</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="0"/>
+        <v>0.15539452495974235</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31">
+        <v>8.24</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="0"/>
+        <v>0.13328729281767954</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32">
+        <v>6.7</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="0"/>
+        <v>0.16929824561403509</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33">
+        <v>4.74</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="0"/>
+        <v>0.25802139037433153</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" t="s">
+        <v>43</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34">
+        <v>7.72</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="0"/>
+        <v>0.14360119047619047</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" t="s">
+        <v>43</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35">
+        <v>5.41</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="0"/>
+        <v>0.21882086167800452</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" t="s">
+        <v>43</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36">
+        <v>5.66</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="0"/>
+        <v>0.20708154506437768</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" t="s">
+        <v>101</v>
+      </c>
+      <c r="E37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" t="s">
+        <v>43</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37">
+        <v>5.15</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="0"/>
+        <v>0.23253012048192767</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" t="s">
+        <v>102</v>
+      </c>
+      <c r="E38" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38">
+        <v>9.27</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" t="s">
+        <v>103</v>
+      </c>
+      <c r="E39" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" t="s">
+        <v>43</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39">
+        <v>6.18</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="0"/>
+        <v>0.18629343629343631</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" t="s">
+        <v>104</v>
+      </c>
+      <c r="E40" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40">
+        <v>7.21</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="0"/>
+        <v>0.15539452495974235</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" t="s">
+        <v>106</v>
+      </c>
+      <c r="E41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41">
+        <v>5.66</v>
+      </c>
+      <c r="N41">
+        <v>1</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="0"/>
+        <v>0.20708154506437768</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" t="s">
+        <v>108</v>
+      </c>
+      <c r="E42" t="s">
+        <v>42</v>
+      </c>
+      <c r="F42" t="s">
+        <v>43</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="N42">
+        <v>1</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="0"/>
+        <v>0.24807197943444731</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43" t="s">
+        <v>110</v>
+      </c>
+      <c r="E43" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" t="s">
+        <v>43</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43">
+        <v>5.41</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="0"/>
+        <v>0.21882086167800452</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" t="s">
+        <v>112</v>
+      </c>
+      <c r="D44" t="s">
+        <v>113</v>
+      </c>
+      <c r="E44" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" t="s">
+        <v>43</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44">
+        <v>5.15</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="0"/>
+        <v>0.23253012048192767</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" t="s">
+        <v>114</v>
+      </c>
+      <c r="E45" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" t="s">
+        <v>43</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="0"/>
+        <v>0.24807197943444731</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46" t="s">
+        <v>117</v>
+      </c>
+      <c r="E46" t="s">
+        <v>42</v>
+      </c>
+      <c r="F46" t="s">
+        <v>43</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="0"/>
+        <v>0.26510989010989011</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>115</v>
+      </c>
+      <c r="C47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47" t="s">
+        <v>119</v>
+      </c>
+      <c r="E47" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" t="s">
+        <v>43</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="0"/>
+        <v>0.24807197943444731</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48" t="s">
+        <v>120</v>
+      </c>
+      <c r="E48" t="s">
+        <v>42</v>
+      </c>
+      <c r="F48" t="s">
+        <v>43</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="N48">
+        <v>1</v>
+      </c>
+      <c r="O48">
+        <f t="shared" si="0"/>
+        <v>0.26510989010989011</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>115</v>
+      </c>
+      <c r="C49" t="s">
+        <v>27</v>
+      </c>
+      <c r="D49" t="s">
+        <v>121</v>
+      </c>
+      <c r="E49" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49" t="s">
+        <v>43</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49">
+        <v>6.18</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="0"/>
+        <v>0.18629343629343631</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>115</v>
+      </c>
+      <c r="C50" t="s">
+        <v>122</v>
+      </c>
+      <c r="D50" t="s">
+        <v>123</v>
+      </c>
+      <c r="E50" t="s">
+        <v>42</v>
+      </c>
+      <c r="F50" t="s">
+        <v>43</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50">
+        <v>5.66</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="0"/>
+        <v>0.20708154506437768</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>124</v>
+      </c>
+      <c r="C51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D51" t="s">
+        <v>126</v>
+      </c>
+      <c r="E51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" t="s">
+        <v>43</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51">
+        <v>6.08</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" t="s">
+        <v>127</v>
+      </c>
+      <c r="D52" t="s">
+        <v>128</v>
+      </c>
+      <c r="E52" t="s">
+        <v>42</v>
+      </c>
+      <c r="F52" t="s">
+        <v>43</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52">
+        <v>6.8</v>
+      </c>
+      <c r="N52">
+        <v>1</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="0"/>
+        <v>0.16637931034482759</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" t="s">
+        <v>129</v>
+      </c>
+      <c r="D53" t="s">
+        <v>130</v>
+      </c>
+      <c r="E53" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" t="s">
+        <v>43</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53">
+        <v>5.67</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="0"/>
+        <v>0.20663811563169165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>131</v>
+      </c>
+      <c r="C54" t="s">
+        <v>40</v>
+      </c>
+      <c r="D54" t="s">
+        <v>132</v>
+      </c>
+      <c r="E54" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" t="s">
+        <v>43</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54">
+        <v>6.18</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+      <c r="O54">
+        <f t="shared" si="0"/>
+        <v>0.18629343629343631</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55" t="s">
+        <v>133</v>
+      </c>
+      <c r="E55" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" t="s">
+        <v>43</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55">
+        <v>6.59</v>
+      </c>
+      <c r="N55">
+        <v>1</v>
+      </c>
+      <c r="O55">
+        <f t="shared" si="0"/>
+        <v>0.17262969588550983</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" t="s">
+        <v>134</v>
+      </c>
+      <c r="E56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F56" t="s">
+        <v>43</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56">
+        <v>5.77</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" t="s">
+        <v>135</v>
+      </c>
+      <c r="D57" t="s">
+        <v>136</v>
+      </c>
+      <c r="E57" t="s">
+        <v>42</v>
+      </c>
+      <c r="F57" t="s">
+        <v>43</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57">
+        <v>5.46</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>137</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" t="s">
+        <v>42</v>
+      </c>
+      <c r="F58" t="s">
+        <v>43</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58">
+        <v>5.25</v>
+      </c>
+      <c r="N58">
+        <v>1</v>
+      </c>
+      <c r="O58">
+        <f t="shared" si="0"/>
+        <v>0.22705882352941176</v>
       </c>
     </row>
   </sheetData>
